--- a/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
+++ b/EX_GAS_Config/ProjectConfigTable/exgas_config/Datas/#exgas.timelineAbility.xlsx
@@ -462,7 +462,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y19"/>
+  <dimension ref="A1:Y18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="16.25" customWidth="1" style="4" min="3" max="3"/>
@@ -1102,101 +1102,72 @@
     <row r="16">
       <c r="F16" t="inlineStr">
         <is>
-          <t>功能轨道1</t>
+          <t>功能轨道2</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H16" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>闪避Task逻辑</t>
+          <t>执行消耗</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>DodgeMove</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>10</v>
-      </c>
-      <c r="L16" t="n">
-        <v>5</v>
+          <t>ApplyCost</t>
+        </is>
       </c>
     </row>
     <row r="17">
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>功能轨道2</t>
-        </is>
-      </c>
       <c r="G17" t="n">
         <v>5</v>
       </c>
       <c r="H17" t="n">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>执行消耗</t>
+          <t>添加无敌帧</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>ApplyCost</t>
+          <t>ApplyEffects</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>1003</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>CatchSelf</t>
         </is>
       </c>
     </row>
     <row r="18">
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>功能轨道3</t>
+        </is>
+      </c>
       <c r="G18" t="n">
         <v>5</v>
       </c>
       <c r="H18" t="n">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>添加无敌帧</t>
+          <t>执行Cooldown冷却</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
-        <is>
-          <t>ApplyEffects</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>1003</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>CatchSelf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>功能轨道3</t>
-        </is>
-      </c>
-      <c r="G19" t="n">
-        <v>5</v>
-      </c>
-      <c r="H19" t="n">
-        <v>5</v>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>执行Cooldown冷却</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
         <is>
           <t>ApplyCooldown</t>
         </is>
